--- a/大富翁/quiz.xlsx
+++ b/大富翁/quiz.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kentxchang\Desktop\www\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kentxchang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FC2F90-F1D9-4E45-9353-52A110539BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD0B920-857F-E64E-82F5-9C1B280687B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="2820" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{C9731CC1-EF9F-4BF5-852E-96960094D522}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C9731CC1-EF9F-4BF5-852E-96960094D522}"/>
   </bookViews>
   <sheets>
     <sheet name="社會題庫工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="英文單字7題" sheetId="4" r:id="rId2"/>
+    <sheet name="英文" sheetId="4" r:id="rId2"/>
     <sheet name="成功課程" sheetId="2" r:id="rId3"/>
     <sheet name="陳樹菊" sheetId="3" r:id="rId4"/>
     <sheet name="陳樹菊(文本)" sheetId="5" r:id="rId5"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="384">
   <si>
     <t>下列何者屬於皇民化運動推行的內容？　</t>
   </si>
@@ -1019,111 +1019,6 @@
   </si>
   <si>
     <t>只有假日</t>
-  </si>
-  <si>
-    <t>book 的中文意思是？</t>
-  </si>
-  <si>
-    <t>書本</t>
-  </si>
-  <si>
-    <t>書包</t>
-  </si>
-  <si>
-    <t>書桌</t>
-  </si>
-  <si>
-    <t>書店</t>
-  </si>
-  <si>
-    <t>apple 的中文意思是？</t>
-  </si>
-  <si>
-    <t>香蕉</t>
-  </si>
-  <si>
-    <t>蘋果</t>
-  </si>
-  <si>
-    <t>梨子</t>
-  </si>
-  <si>
-    <t>葡萄</t>
-  </si>
-  <si>
-    <t>dog 的中文意思是？</t>
-  </si>
-  <si>
-    <t>貓</t>
-  </si>
-  <si>
-    <t>老虎</t>
-  </si>
-  <si>
-    <t>狗</t>
-  </si>
-  <si>
-    <t>獅子</t>
-  </si>
-  <si>
-    <t>water 的中文意思是？</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>牛奶</t>
-  </si>
-  <si>
-    <t>果汁</t>
-  </si>
-  <si>
-    <t>湯</t>
-  </si>
-  <si>
-    <t>chair 的中文意思是？</t>
-  </si>
-  <si>
-    <t>桌子</t>
-  </si>
-  <si>
-    <t>椅子</t>
-  </si>
-  <si>
-    <t>床</t>
-  </si>
-  <si>
-    <t>沙發</t>
-  </si>
-  <si>
-    <t>happy 的中文意思是？</t>
-  </si>
-  <si>
-    <t>傷心</t>
-  </si>
-  <si>
-    <t>生氣</t>
-  </si>
-  <si>
-    <t>快樂</t>
-  </si>
-  <si>
-    <t>害怕</t>
-  </si>
-  <si>
-    <t>run 的中文意思是？</t>
-  </si>
-  <si>
-    <t>跳</t>
-  </si>
-  <si>
-    <t>坐</t>
-  </si>
-  <si>
-    <t>走</t>
-  </si>
-  <si>
-    <t>跑</t>
   </si>
   <si>
     <t>73歲陳樹菊退休狂讀書 阿嬤霸氣說：把沒讀的書讀回來
@@ -1135,12 +1030,220 @@
 阿嬤也說，自己現在沒有做生意了，可以做很多想做的事，但沒生意做也代表沒錢賺，所以存的錢相對比較少一點，她也就量力而為來捐款，能捐多少算多少，因為她不是「好小白浪（台語語意：唬爛吹牛）的人。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>餐廳的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restaurant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bookstore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>park</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hospital</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公園的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bakery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超市的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supermarket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>書局的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>銀行的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麵包店的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>醫院的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郵局的英文單字是?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>post office</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He ___ going to the park.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>am</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>are</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>She ___ going to the bookstore.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We ___ going to the park.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amy and I  ___ going to the park.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I ___ going to the bakery.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amy ___ going to the supermarket.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They ___ going to the supermarket.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>___ is going to the restaurant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>___ am going to the restaurant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>___ are going to the restaurant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ben</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ben and I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ben and Ken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I am ___  to the bakery.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>go</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>going</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ben and Lisa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>She</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restaurant</t>
+  </si>
+  <si>
+    <t>bookstore</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>題目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>答案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選項1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選項2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選項3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選項4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1204,9 +1307,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1244,7 +1347,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1350,7 +1453,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1492,7 +1595,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1500,1006 +1603,1026 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11AE548-B82B-48CA-ACC2-A09A0380DECC}">
-  <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>0</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>33</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>37</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>40</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>45</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>47</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>50</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>52</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>53</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>55</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>58</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>47</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>59</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>61</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>62</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>63</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>66</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>67</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>68</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>69</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
         <v>71</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>4</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>46</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
         <v>72</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>77</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>84</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E20" t="s">
         <v>85</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
         <v>87</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>88</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>67</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>89</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
         <v>91</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>96</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
         <v>102</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>103</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>52</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
         <v>105</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>4</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>106</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>107</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>108</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
         <v>110</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>111</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>112</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E26" t="s">
         <v>113</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>115</v>
-      </c>
-      <c r="B26">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>116</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
         <v>117</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>118</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>119</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
         <v>121</v>
-      </c>
-      <c r="B28">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>126</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
         <v>46</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>47</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>48</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
         <v>127</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>132</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
         <v>133</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>134</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>135</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F32" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
         <v>137</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>1</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>138</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>139</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>140</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
         <v>142</v>
-      </c>
-      <c r="B33">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" t="s">
-        <v>144</v>
-      </c>
-      <c r="E33" t="s">
-        <v>145</v>
-      </c>
-      <c r="F33" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>147</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
       <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" t="s">
+        <v>145</v>
+      </c>
+      <c r="F34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
         <v>148</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>149</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E35" t="s">
         <v>150</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
         <v>152</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>2</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>153</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>154</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>155</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F36" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
         <v>157</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>4</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>158</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>159</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E37" t="s">
         <v>160</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
         <v>162</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>2</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>48</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>59</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E38" t="s">
         <v>47</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F38" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
         <v>164</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>3</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>165</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>8</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E39" t="s">
         <v>166</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
         <v>168</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>4</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>46</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>47</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E40" t="s">
         <v>48</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F40" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
         <v>169</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>3</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>170</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>171</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>172</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F41" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
         <v>174</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>4</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>46</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>47</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>48</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
         <v>175</v>
-      </c>
-      <c r="B42">
-        <v>2</v>
-      </c>
-      <c r="C42" t="s">
-        <v>176</v>
-      </c>
-      <c r="D42" t="s">
-        <v>177</v>
-      </c>
-      <c r="E42" t="s">
-        <v>178</v>
-      </c>
-      <c r="F42" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>180</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D43" t="s">
+        <v>177</v>
+      </c>
+      <c r="E43" t="s">
+        <v>178</v>
+      </c>
+      <c r="F43" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
         <v>181</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>182</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E44" t="s">
         <v>183</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F44" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
         <v>185</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>4</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>186</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>187</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E45" t="s">
         <v>188</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F45" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
         <v>190</v>
-      </c>
-      <c r="B45">
-        <v>3</v>
-      </c>
-      <c r="C45" t="s">
-        <v>191</v>
-      </c>
-      <c r="D45" t="s">
-        <v>192</v>
-      </c>
-      <c r="E45" t="s">
-        <v>193</v>
-      </c>
-      <c r="F45" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>195</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E46" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F46" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" t="s">
+        <v>197</v>
+      </c>
+      <c r="E47" t="s">
+        <v>198</v>
+      </c>
+      <c r="F47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
         <v>46</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>47</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E48" t="s">
         <v>59</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F48" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
         <v>201</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>2</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>202</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>203</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E49" t="s">
         <v>204</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
         <v>206</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>3</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>207</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>208</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E50" t="s">
         <v>209</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F50" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
         <v>211</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>1</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>212</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>213</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E51" t="s">
         <v>214</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F51" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2511,270 +2634,533 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05037C2F-DD55-42C2-91C0-866DFB2DCBFD}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="6" width="11.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B1" s="1">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="26" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>338</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="26" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B3" s="1">
+      <c r="F4" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="26" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="26" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="26" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="26" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="26" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="26" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B5" s="1">
+      <c r="F10" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="26" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="26" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="26" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B14" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="26" customHeight="1">
+      <c r="A15" s="1" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="B15" s="1">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="26" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="26" customHeight="1">
+      <c r="A17" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F17" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="26" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B7" s="1">
+      <c r="E18" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="26" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B19" s="1">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+    <row r="20" spans="1:6" ht="26" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="26" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>371</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" copies="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{849B4F66-5B23-4A25-87B1-A3E56572C1B3}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>216</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>217</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>218</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>219</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>221</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>226</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>227</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>228</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>229</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>231</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>232</v>
@@ -2789,183 +3175,203 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>237</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>238</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>239</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>240</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>242</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>243</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>244</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>245</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>247</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>248</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>249</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>250</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>252</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>253</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>254</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>255</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>257</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>258</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>259</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>260</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>262</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>263</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>264</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>265</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>267</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>268</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>229</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>228</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>270</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>271</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>272</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>273</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>275</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>276</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>277</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>278</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>279</v>
       </c>
     </row>
@@ -2977,206 +3383,226 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD230FFA-E208-44DF-82B2-98857156C7A5}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="48">
+      <c r="A2" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:6" ht="48">
+      <c r="A3" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="81" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:6" ht="64">
+      <c r="A4" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="81" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:6" ht="64">
+      <c r="A5" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:6" ht="48">
+      <c r="A6" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:6" ht="64">
+      <c r="A7" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="81" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:6" ht="64">
+      <c r="A8" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:6" ht="80">
+      <c r="A9" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:6" ht="80">
+      <c r="A10" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:6" ht="80">
+      <c r="A11" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>2</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>329</v>
       </c>
     </row>
@@ -3189,11 +3615,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC63F73D-E6FD-4B11-AB61-F230F877CB40}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="409.6">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
